--- a/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
+++ b/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>mix_change_effect</t>
+          <t>concentration_change_effect</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.024145</v>
+        <v>0.047935</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02694</v>
+        <v>0.051686</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002144</v>
+        <v>0.001162</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00065</v>
+        <v>0.002588</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.16703</v>
+        <v>0.362579</v>
       </c>
       <c r="C3" t="n">
-        <v>0.183428</v>
+        <v>0.390944</v>
       </c>
       <c r="D3" t="n">
-        <v>0.011937</v>
+        <v>0.008788000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004461</v>
+        <v>0.019577</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.280076</v>
+        <v>0.559982</v>
       </c>
       <c r="C4" t="n">
-        <v>0.303457</v>
+        <v>0.603789</v>
       </c>
       <c r="D4" t="n">
-        <v>0.015952</v>
+        <v>0.013573</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007429</v>
+        <v>0.030235</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
+++ b/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.047935</v>
+        <v>0.054537</v>
       </c>
       <c r="C2" t="n">
-        <v>0.051686</v>
+        <v>0.059271</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001162</v>
+        <v>0.001038</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002588</v>
+        <v>0.003697</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.362579</v>
+        <v>0.370035</v>
       </c>
       <c r="C3" t="n">
-        <v>0.390944</v>
+        <v>0.402157</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008788000000000001</v>
+        <v>0.00704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.019577</v>
+        <v>0.025082</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.559982</v>
+        <v>0.592711</v>
       </c>
       <c r="C4" t="n">
-        <v>0.603789</v>
+        <v>0.644163</v>
       </c>
       <c r="D4" t="n">
-        <v>0.013573</v>
+        <v>0.011277</v>
       </c>
       <c r="E4" t="n">
-        <v>0.030235</v>
+        <v>0.040176</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
+++ b/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.054537</v>
+        <v>0.05295</v>
       </c>
       <c r="C2" t="n">
-        <v>0.059271</v>
+        <v>0.057592</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001038</v>
+        <v>0.000954</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003697</v>
+        <v>0.003688</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.370035</v>
+        <v>0.337393</v>
       </c>
       <c r="C3" t="n">
-        <v>0.402157</v>
+        <v>0.366969</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00704</v>
+        <v>0.006077</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025082</v>
+        <v>0.023499</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.592711</v>
+        <v>0.593262</v>
       </c>
       <c r="C4" t="n">
-        <v>0.644163</v>
+        <v>0.645267</v>
       </c>
       <c r="D4" t="n">
-        <v>0.011277</v>
+        <v>0.010686</v>
       </c>
       <c r="E4" t="n">
-        <v>0.040176</v>
+        <v>0.04132</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
+++ b/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05295</v>
+        <v>0.056059</v>
       </c>
       <c r="C2" t="n">
-        <v>0.057592</v>
+        <v>0.06086</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000954</v>
+        <v>0.00099</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003688</v>
+        <v>0.003811</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.337393</v>
+        <v>0.337718</v>
       </c>
       <c r="C3" t="n">
-        <v>0.366969</v>
+        <v>0.366637</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006077</v>
+        <v>0.005962</v>
       </c>
       <c r="E3" t="n">
-        <v>0.023499</v>
+        <v>0.022957</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.593262</v>
+        <v>0.525852</v>
       </c>
       <c r="C4" t="n">
-        <v>0.645267</v>
+        <v>0.570881</v>
       </c>
       <c r="D4" t="n">
-        <v>0.010686</v>
+        <v>0.009284000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04132</v>
+        <v>0.035746</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
+++ b/vignettes/vignette-2/old_to_new_change_decomposition.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.056059</v>
+        <v>0.05608</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06086</v>
+        <v>0.060877</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00099</v>
+        <v>0.000975</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003811</v>
+        <v>0.003822</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.337718</v>
+        <v>0.337412</v>
       </c>
       <c r="C3" t="n">
-        <v>0.366637</v>
+        <v>0.366273</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005962</v>
+        <v>0.005867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.022957</v>
+        <v>0.022995</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.525852</v>
+        <v>0.526157</v>
       </c>
       <c r="C4" t="n">
-        <v>0.570881</v>
+        <v>0.571163</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009284000000000001</v>
+        <v>0.009148</v>
       </c>
       <c r="E4" t="n">
-        <v>0.035746</v>
+        <v>0.035857</v>
       </c>
     </row>
   </sheetData>
